--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513087_ELIMINATORIAS14FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513087_ELIMINATORIAS14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.575</v>
+        <v>1.5592</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0152</v>
+        <v>4.9978</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.4401</v>
+        <v>-3.4386</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2364</v>
+        <v>-0.2407</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9977</v>
+        <v>-0.9888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7613</v>
+        <v>0.7481</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1766</v>
+        <v>3.2528</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6476</v>
+        <v>0.7085</v>
       </c>
       <c r="L2" t="n">
-        <v>2.529</v>
+        <v>2.5443</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.413</v>
+        <v>-3.4935</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6453</v>
+        <v>-1.6973</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7677</v>
+        <v>-1.7962</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4562</v>
+        <v>-0.5676</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9113</v>
+        <v>-0.2183</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4551</v>
+        <v>-0.3493</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3553</v>
+        <v>2.3675</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5962</v>
+        <v>-0.608</v>
       </c>
     </row>
     <row r="3">
@@ -643,31 +643,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4782</v>
+        <v>1.489</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4782</v>
+        <v>1.489</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4782</v>
+        <v>1.489</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1855</v>
+        <v>1.1926</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4782</v>
+        <v>1.489</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1855</v>
+        <v>1.1926</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8563</v>
+        <v>-0.4991</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2242</v>
+        <v>0.7301</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0806</v>
+        <v>-1.2291</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3478</v>
+        <v>-0.37</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7954</v>
+        <v>-1.8175</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4475</v>
+        <v>1.4474</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5908</v>
+        <v>1.6115</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3455</v>
+        <v>-0.3365</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9362</v>
+        <v>1.948</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9386</v>
+        <v>-1.9815</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4499</v>
+        <v>-1.481</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4887</v>
+        <v>-0.5006</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.2825</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.655</v>
+        <v>-0.2251</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0386</v>
+        <v>-0.0574</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9351</v>
+        <v>-0.8861</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0725</v>
+        <v>-0.0688</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8626</v>
+        <v>-0.8173</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.704</v>
+        <v>-0.7157</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3318</v>
+        <v>-0.3358</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3722</v>
+        <v>-0.3798</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0585</v>
+        <v>0.0593</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0585</v>
+        <v>0.0593</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7625</v>
+        <v>-0.7749</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3903</v>
+        <v>-0.3951</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3722</v>
+        <v>-0.3798</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.231</v>
+        <v>-0.1704</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1001</v>
+        <v>-0.0424</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.417</v>
+        <v>-1.8259</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3919</v>
+        <v>2.004</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.8088</v>
+        <v>-3.83</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.184</v>
+        <v>-3.2266</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7594</v>
+        <v>-1.7969</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4246</v>
+        <v>-1.4297</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0374</v>
+        <v>1.0773</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4156</v>
+        <v>0.4339</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6218</v>
+        <v>0.6433</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.2214</v>
+        <v>-4.3039</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.175</v>
+        <v>-2.2308</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0464</v>
+        <v>-2.0731</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1785</v>
+        <v>-0.5619</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9825</v>
+        <v>-0.4414</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.196</v>
+        <v>-0.1205</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3553</v>
+        <v>2.3675</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0059</v>
+        <v>-0.0129</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.0497</v>
+        <v>-2.4932</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4686</v>
+        <v>0.1438</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5811</v>
+        <v>-2.637</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5513</v>
+        <v>-2.6027</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5263</v>
+        <v>-2.5864</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.025</v>
+        <v>-0.0163</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1688</v>
+        <v>1.2255</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1229</v>
+        <v>0.1376</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0459</v>
+        <v>1.0879</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.7201</v>
+        <v>-3.8282</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.6492</v>
+        <v>-2.7241</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0709</v>
+        <v>-1.1041</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.3421</v>
+        <v>-1.7126</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.6374</v>
+        <v>-1.0817</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7047</v>
+        <v>-0.6309</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4773</v>
+        <v>-2.9591</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5677</v>
+        <v>-2.115</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9096</v>
+        <v>-0.844</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2755</v>
+        <v>-3.2837</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.5226</v>
+        <v>-2.5298</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7529</v>
+        <v>-0.7539</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9782</v>
+        <v>-1.954</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9927</v>
+        <v>-1.9775</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0145</v>
+        <v>0.0235</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2973</v>
+        <v>-1.3297</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5299</v>
+        <v>-0.5523</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7674</v>
+        <v>-0.7774</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2572</v>
+        <v>0.2768</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5895</v>
+        <v>-0.161</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3322</v>
+        <v>0.4379</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3542</v>
+        <v>-0.3571</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3542</v>
+        <v>-0.3571</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4738</v>
+        <v>-4.1835</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.568</v>
+        <v>-1.2427</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9059</v>
+        <v>-2.9409</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9169</v>
+        <v>-0.9409</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4013</v>
+        <v>-0.4268</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4829</v>
+        <v>1.5399</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3249</v>
+        <v>1.3809</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1581</v>
+        <v>0.159</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3998</v>
+        <v>-2.4807</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8405</v>
+        <v>-1.8949</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5593</v>
+        <v>-0.5859</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9979</v>
+        <v>-1.6832</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2445</v>
+        <v>-1.009</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7534</v>
+        <v>-0.6742</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9445</v>
+        <v>-0.9522</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1865</v>
+        <v>-1.2031</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.587</v>
+        <v>-4.2512</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8404</v>
+        <v>-1.4743</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7466</v>
+        <v>-2.7769</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2205</v>
+        <v>-3.0436</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6815</v>
+        <v>-3.8343</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.539</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2687</v>
+        <v>-0.1487</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4268</v>
+        <v>-2.0967</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1581</v>
+        <v>1.948</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9518</v>
+        <v>-2.8949</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2548</v>
+        <v>-1.7376</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6971</v>
+        <v>-1.1572</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.663</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0727</v>
+        <v>-1.0123</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="S10" t="n">
-        <v>2.993</v>
+        <v>-0.5996</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1975</v>
+        <v>-0.3133</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7955</v>
+        <v>-0.2862</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6965</v>
+        <v>-0.608</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6965</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.608</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6959</v>
+        <v>-6.3939</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.063</v>
+        <v>-4.232</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6329</v>
+        <v>-2.1619</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0278</v>
+        <v>-4.2399</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.8244</v>
+        <v>-2.688</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7966</v>
+        <v>-1.5519</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1873</v>
+        <v>-1.2456</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1235</v>
+        <v>-1.4046</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9362</v>
+        <v>0.159</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8405</v>
+        <v>-2.9943</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7009</v>
+        <v>-1.2834</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1396</v>
+        <v>-1.7109</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.6319</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>-3.0368</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0719</v>
+        <v>1.1662</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8515</v>
+        <v>0.7387</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2204</v>
+        <v>0.4275</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5962</v>
+        <v>-0.6883</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6883</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.9188</v>
+        <v>-7.9484</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5743</v>
+        <v>-4.426</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3446</v>
+        <v>-3.5223</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9952</v>
+        <v>-4.0011</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8759</v>
+        <v>-1.8778</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1193</v>
+        <v>-2.1233</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7822</v>
+        <v>-0.7075</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0354</v>
+        <v>0.0171</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7468</v>
+        <v>-0.7246</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.213</v>
+        <v>-3.2935</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8405</v>
+        <v>-1.8949</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3725</v>
+        <v>-1.3987</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2029</v>
+        <v>-1.2467</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6132</v>
+        <v>-0.5885</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5897</v>
+        <v>-0.6582</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2868</v>
+        <v>-1.2834</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1062</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-28.3577</v>
+        <v>-28.3922</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.045</v>
+        <v>-4.194100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-23.3128</v>
+        <v>-24.198</v>
       </c>
       <c r="G13" t="n">
-        <v>-20.9812</v>
+        <v>-21.1759</v>
       </c>
       <c r="H13" t="n">
-        <v>-18.5379</v>
+        <v>-18.673</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.4434</v>
+        <v>-2.5028</v>
       </c>
       <c r="J13" t="n">
-        <v>5.776800000000001</v>
+        <v>6.199500000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.0617</v>
+        <v>-2.7817</v>
       </c>
       <c r="L13" t="n">
-        <v>8.8385</v>
+        <v>8.981</v>
       </c>
       <c r="M13" t="n">
-        <v>-26.758</v>
+        <v>-27.3751</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.4763</v>
+        <v>-15.8914</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.2818</v>
+        <v>-11.4839</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.1211</v>
+        <v>-5.0614</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.3392</v>
+        <v>-14.1718</v>
       </c>
       <c r="R13" t="n">
-        <v>9.218</v>
+        <v>9.110499999999998</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.448700000000001</v>
+        <v>-5.381499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5958</v>
+        <v>-3.4277</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8531</v>
+        <v>-1.9537</v>
       </c>
       <c r="V13" t="n">
-        <v>3.1936</v>
+        <v>3.2264</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1133</v>
+        <v>7.205699999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.9196</v>
+        <v>-3.9793</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1092</v>
+        <v>5.64</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7783</v>
+        <v>2.401</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3309</v>
+        <v>3.239</v>
       </c>
       <c r="G14" t="n">
-        <v>2.012</v>
+        <v>2.0481</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3031</v>
+        <v>2.3499</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2911</v>
+        <v>-0.3018</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4697</v>
+        <v>1.5395</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2721</v>
+        <v>1.3407</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1976</v>
+        <v>0.1988</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5423</v>
+        <v>0.5087</v>
       </c>
       <c r="N14" t="n">
-        <v>1.031</v>
+        <v>1.0092</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4887</v>
+        <v>-0.5006</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3523</v>
+        <v>0.879</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0666</v>
+        <v>0.6106</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2857</v>
+        <v>0.2684</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4544</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.615</v>
+        <v>5.3134</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9687</v>
+        <v>3.9607</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6463</v>
+        <v>1.3527</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5176</v>
+        <v>3.5497</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0015</v>
+        <v>2.0155</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5161</v>
+        <v>1.5342</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3843</v>
+        <v>4.4891</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8908</v>
+        <v>1.9537</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4935</v>
+        <v>2.5353</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8667</v>
+        <v>-0.9393</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1107</v>
+        <v>0.0618</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9774</v>
+        <v>-1.0011</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R15" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4829</v>
+        <v>1.1563</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5477</v>
+        <v>0.306</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0306</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2598</v>
+        <v>3.9467</v>
       </c>
       <c r="E16" t="n">
-        <v>5.8697</v>
+        <v>1.7686</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.61</v>
+        <v>2.1781</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6877</v>
+        <v>1.7998</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7692</v>
+        <v>1.897</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0814</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9951</v>
+        <v>1.8661</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7975</v>
+        <v>1.342</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1976</v>
+        <v>0.5241</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3073</v>
+        <v>-0.0663</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0283</v>
+        <v>0.555</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.279</v>
+        <v>-0.6213</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4097</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6145</v>
+        <v>2.0245</v>
       </c>
       <c r="S16" t="n">
-        <v>2.572</v>
+        <v>0.6125</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0666</v>
+        <v>0.1417</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4708</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5903</v>
+        <v>1.5344</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8324</v>
+        <v>1.7853</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4227</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3454</v>
+        <v>3.4781</v>
       </c>
       <c r="E17" t="n">
-        <v>3.906</v>
+        <v>4.1787</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5606</v>
+        <v>-0.7005</v>
       </c>
       <c r="G17" t="n">
-        <v>4.0439</v>
+        <v>4.053</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9056</v>
+        <v>0.8903</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1383</v>
+        <v>3.1627</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3232</v>
+        <v>5.3675</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4879</v>
+        <v>0.4939</v>
       </c>
       <c r="L17" t="n">
-        <v>4.8354</v>
+        <v>4.8736</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2793</v>
+        <v>-1.3145</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4178</v>
+        <v>0.3964</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6971</v>
+        <v>-1.7109</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4937</v>
+        <v>-0.3724</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.393</v>
+        <v>-0.1766</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1007</v>
+        <v>-0.1958</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0363</v>
+        <v>3.3777</v>
       </c>
       <c r="E18" t="n">
-        <v>2.842</v>
+        <v>3.2415</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1942</v>
+        <v>0.1362</v>
       </c>
       <c r="G18" t="n">
-        <v>4.2223</v>
+        <v>4.2395</v>
       </c>
       <c r="H18" t="n">
-        <v>2.623</v>
+        <v>2.6287</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5993</v>
+        <v>1.6108</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5213</v>
+        <v>4.5827</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8988</v>
+        <v>1.9353</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6225</v>
+        <v>2.6473</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.299</v>
+        <v>-0.3431</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7242</v>
+        <v>0.6934</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0232</v>
+        <v>-1.0365</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2103</v>
+        <v>0.126</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.655</v>
+        <v>-0.3289</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4447</v>
+        <v>0.4548</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6811</v>
+        <v>2.9078</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7584</v>
+        <v>2.0757</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9228</v>
+        <v>0.8321</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2486</v>
+        <v>2.2778</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8934</v>
+        <v>2.9052</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6448</v>
+        <v>-0.6274</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1295</v>
+        <v>2.2056</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3086</v>
+        <v>2.3502</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.179</v>
+        <v>-0.1445</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1191</v>
+        <v>0.0722</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5849</v>
+        <v>0.555</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3226</v>
+        <v>1.5447</v>
       </c>
       <c r="T19" t="n">
-        <v>0.411</v>
+        <v>0.6313</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9116</v>
+        <v>0.9134</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1191</v>
+        <v>-2.1295</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.6491</v>
+        <v>2.6239</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6082</v>
+        <v>4.41</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0409</v>
+        <v>-1.7861</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7825</v>
+        <v>2.716</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8844</v>
+        <v>3.8128</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1019</v>
+        <v>-1.0969</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8028</v>
+        <v>4.0694</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2996</v>
+        <v>3.8706</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5032</v>
+        <v>0.1988</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0203</v>
+        <v>-1.3535</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5849</v>
+        <v>-0.0578</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6051</v>
+        <v>-1.2957</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0485</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6622</v>
+        <v>0.908</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.917</v>
+        <v>0.5068</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2548</v>
+        <v>0.4012</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5288</v>
+        <v>-0.5951</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7709</v>
+        <v>0.846</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2421</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.1015</v>
+        <v>2.4954</v>
       </c>
       <c r="E21" t="n">
-        <v>4.4377</v>
+        <v>4.8108</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3363</v>
+        <v>-2.3154</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2315</v>
+        <v>3.2404</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1108</v>
+        <v>3.1226</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1206</v>
+        <v>0.1178</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8962</v>
+        <v>4.9476</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4737</v>
+        <v>3.5164</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4225</v>
+        <v>1.4312</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6647</v>
+        <v>-1.7071</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3628</v>
+        <v>-0.3938</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3019</v>
+        <v>-1.3134</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7688</v>
+        <v>-0.3646</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4585</v>
+        <v>-0.1368</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3103</v>
+        <v>-0.2279</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3759</v>
+        <v>0.3372</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3444</v>
+        <v>-1.1517</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7203</v>
+        <v>1.489</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1606</v>
+        <v>-1.1428</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8361</v>
+        <v>-0.8305</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3245</v>
+        <v>-0.3122</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4484</v>
+        <v>-0.3868</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3339</v>
+        <v>-0.2983</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1145</v>
+        <v>-0.0885</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.7559</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5022</v>
+        <v>-0.5322</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.21</v>
+        <v>-0.2237</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2702</v>
+        <v>1.2168</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4765</v>
+        <v>0.5915</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7937</v>
+        <v>0.6253</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8155</v>
+        <v>-1.7281</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5119</v>
+        <v>-1.4973</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3036</v>
+        <v>-0.2309</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6041</v>
+        <v>-1.6057</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1171</v>
+        <v>-0.1185</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4871</v>
+        <v>-1.4872</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3155</v>
+        <v>-1.3052</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6187</v>
+        <v>-0.6131</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2887</v>
+        <v>-0.3006</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5016</v>
+        <v>0.4945</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7903</v>
+        <v>-0.7951</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4162</v>
+        <v>-0.3249</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1965</v>
+        <v>-0.1921</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2198</v>
+        <v>-0.1328</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>28.3578</v>
+        <v>28.3921</v>
       </c>
       <c r="E24" t="n">
-        <v>23.3127</v>
+        <v>24.198</v>
       </c>
       <c r="F24" t="n">
-        <v>5.044899999999999</v>
+        <v>4.1942</v>
       </c>
       <c r="G24" t="n">
-        <v>20.9814</v>
+        <v>21.1758</v>
       </c>
       <c r="H24" t="n">
-        <v>18.5378</v>
+        <v>18.673</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4435</v>
+        <v>2.5028</v>
       </c>
       <c r="J24" t="n">
-        <v>26.7582</v>
+        <v>27.3755</v>
       </c>
       <c r="K24" t="n">
-        <v>15.4764</v>
+        <v>15.8914</v>
       </c>
       <c r="L24" t="n">
-        <v>11.282</v>
+        <v>11.484</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.776800000000001</v>
+        <v>-6.1994</v>
       </c>
       <c r="N24" t="n">
-        <v>3.0618</v>
+        <v>2.7815</v>
       </c>
       <c r="O24" t="n">
-        <v>-8.8385</v>
+        <v>-8.981199999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>5.121099999999999</v>
+        <v>5.0614</v>
       </c>
       <c r="Q24" t="n">
-        <v>-9.218</v>
+        <v>-9.110500000000002</v>
       </c>
       <c r="R24" t="n">
-        <v>14.3393</v>
+        <v>14.1717</v>
       </c>
       <c r="S24" t="n">
-        <v>5.4488</v>
+        <v>5.3814</v>
       </c>
       <c r="T24" t="n">
-        <v>1.853000000000001</v>
+        <v>1.9535</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5958</v>
+        <v>3.4277</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.1935</v>
+        <v>-3.2265</v>
       </c>
       <c r="W24" t="n">
-        <v>3.919900000000001</v>
+        <v>3.9791</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.1134</v>
+        <v>-7.2056</v>
       </c>
     </row>
   </sheetData>
